--- a/testing_files/products/test_products_500_rows.xlsx
+++ b/testing_files/products/test_products_500_rows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\POS PyQt6\testing_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program\POS PyQt6\testing_files\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44822FA0-97E0-46C4-AF9C-8D2D286EB730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65B68DF-E50F-4D43-8761-0643F1B6069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17172" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2421" uniqueCount="1401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3421" uniqueCount="1434">
   <si>
     <t>SKU</t>
   </si>
@@ -4228,6 +4228,105 @@
   </si>
   <si>
     <t>61723077125250</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Global Traders</t>
+  </si>
+  <si>
+    <t>Pet Supplies</t>
+  </si>
+  <si>
+    <t>Style Outfitters</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage</t>
+  </si>
+  <si>
+    <t>I-Store</t>
+  </si>
+  <si>
+    <t>Health &amp; Beauty</t>
+  </si>
+  <si>
+    <t>The Home Store</t>
+  </si>
+  <si>
+    <t>Jewelry &amp; Watches</t>
+  </si>
+  <si>
+    <t>Easy Living</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Home Essentials</t>
+  </si>
+  <si>
+    <t>Style &amp; More</t>
+  </si>
+  <si>
+    <t>Toys &amp; Games</t>
+  </si>
+  <si>
+    <t>Perfect Home</t>
+  </si>
+  <si>
+    <t>Care Products Ltd</t>
+  </si>
+  <si>
+    <t>Stationery</t>
+  </si>
+  <si>
+    <t>Baby &amp; Child</t>
+  </si>
+  <si>
+    <t>Eco Supplies</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Fresh Imports</t>
+  </si>
+  <si>
+    <t>Prime Distributors</t>
+  </si>
+  <si>
+    <t>U-Store</t>
+  </si>
+  <si>
+    <t>Tech Innovators</t>
+  </si>
+  <si>
+    <t>Clothing</t>
+  </si>
+  <si>
+    <t>Home Supplies</t>
+  </si>
+  <si>
+    <t>Bargain Box</t>
+  </si>
+  <si>
+    <t>Garden &amp; Outdoor</t>
+  </si>
+  <si>
+    <t>Beauty &amp; Personal Care</t>
+  </si>
+  <si>
+    <t>All Seasons</t>
+  </si>
+  <si>
+    <t>Office Supplies</t>
+  </si>
+  <si>
+    <t>Art &amp; Crafts</t>
+  </si>
+  <si>
+    <t>Personal Care</t>
   </si>
 </sst>
 </file>
@@ -4391,10 +4490,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:J501"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4420,7 +4519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4445,8 +4544,14 @@
       <c r="H2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4471,8 +4576,14 @@
       <c r="H3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -4491,8 +4602,14 @@
       <c r="G4">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>530</v>
       </c>
@@ -4514,8 +4631,14 @@
       <c r="G5">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -4534,8 +4657,14 @@
       <c r="G6">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -4554,8 +4683,14 @@
       <c r="G7">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -4577,8 +4712,14 @@
       <c r="H8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -4597,8 +4738,14 @@
       <c r="G9">
         <v>88</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -4620,8 +4767,14 @@
       <c r="G10">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -4637,8 +4790,14 @@
       <c r="G11">
         <v>99</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -4663,8 +4822,14 @@
       <c r="H12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -4686,8 +4851,14 @@
       <c r="H13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4712,8 +4883,14 @@
       <c r="H14" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
@@ -4738,8 +4915,14 @@
       <c r="H15" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -4761,8 +4944,14 @@
       <c r="H16" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -4784,8 +4973,14 @@
       <c r="H17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -4810,8 +5005,14 @@
       <c r="H18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -4836,8 +5037,14 @@
       <c r="H19" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -4859,8 +5066,14 @@
       <c r="H20" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -4885,8 +5098,14 @@
       <c r="H21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -4905,8 +5124,14 @@
       <c r="G22">
         <v>96</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -4931,8 +5156,14 @@
       <c r="H23" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -4957,8 +5188,14 @@
       <c r="H24" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -4980,8 +5217,14 @@
       <c r="H25" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I25" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -5003,8 +5246,14 @@
       <c r="G26">
         <v>234</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I26" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -5026,8 +5275,14 @@
       <c r="H27" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I27" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>96</v>
       </c>
@@ -5049,8 +5304,14 @@
       <c r="G28">
         <v>403</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I28" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -5075,8 +5336,14 @@
       <c r="H29" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -5101,8 +5368,14 @@
       <c r="H30" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I30" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -5124,8 +5397,14 @@
       <c r="H31" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>108</v>
       </c>
@@ -5150,8 +5429,14 @@
       <c r="H32" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I32" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -5176,8 +5461,14 @@
       <c r="H33" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I33" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>113</v>
       </c>
@@ -5202,8 +5493,14 @@
       <c r="H34" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I34" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -5225,8 +5522,14 @@
       <c r="H35" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>119</v>
       </c>
@@ -5248,8 +5551,14 @@
       <c r="H36" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>121</v>
       </c>
@@ -5271,8 +5580,14 @@
       <c r="H37" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>123</v>
       </c>
@@ -5294,8 +5609,14 @@
       <c r="H38" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>125</v>
       </c>
@@ -5317,8 +5638,14 @@
       <c r="H39" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I39" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -5343,8 +5670,14 @@
       <c r="H40" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>131</v>
       </c>
@@ -5366,8 +5699,14 @@
       <c r="H41" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>133</v>
       </c>
@@ -5392,8 +5731,14 @@
       <c r="H42" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I42" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -5418,8 +5763,14 @@
       <c r="H43" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -5441,8 +5792,14 @@
       <c r="G44">
         <v>441</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I44" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -5467,8 +5824,14 @@
       <c r="H45" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I45" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>144</v>
       </c>
@@ -5493,8 +5856,14 @@
       <c r="H46" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>147</v>
       </c>
@@ -5519,8 +5888,14 @@
       <c r="H47" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I47" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J47" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -5545,8 +5920,14 @@
       <c r="H48" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -5568,8 +5949,14 @@
       <c r="H49" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J49" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -5591,8 +5978,14 @@
       <c r="H50" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I50" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -5614,8 +6007,14 @@
       <c r="H51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I51" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -5637,8 +6036,14 @@
       <c r="H52" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I52" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J52" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>162</v>
       </c>
@@ -5660,8 +6065,14 @@
       <c r="H53" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I53" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J53" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>165</v>
       </c>
@@ -5686,8 +6097,14 @@
       <c r="H54" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J54" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>167</v>
       </c>
@@ -5712,8 +6129,14 @@
       <c r="H55" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>170</v>
       </c>
@@ -5738,8 +6161,14 @@
       <c r="H56" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I56" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J56" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>173</v>
       </c>
@@ -5764,8 +6193,14 @@
       <c r="H57" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I57" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J57" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>176</v>
       </c>
@@ -5784,8 +6219,14 @@
       <c r="G58">
         <v>225</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I58" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>179</v>
       </c>
@@ -5810,8 +6251,14 @@
       <c r="H59" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I59" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>181</v>
       </c>
@@ -5836,8 +6283,14 @@
       <c r="H60" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I60" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>183</v>
       </c>
@@ -5859,8 +6312,14 @@
       <c r="H61" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I61" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J61" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>186</v>
       </c>
@@ -5882,8 +6341,14 @@
       <c r="H62" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I62" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>188</v>
       </c>
@@ -5908,8 +6373,14 @@
       <c r="H63" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J63" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>190</v>
       </c>
@@ -5928,8 +6399,14 @@
       <c r="G64">
         <v>445</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I64" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J64" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>193</v>
       </c>
@@ -5954,8 +6431,14 @@
       <c r="H65" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I65" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>196</v>
       </c>
@@ -5977,8 +6460,14 @@
       <c r="H66" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I66" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>199</v>
       </c>
@@ -6000,8 +6489,14 @@
       <c r="H67" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I67" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J67" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>202</v>
       </c>
@@ -6026,8 +6521,14 @@
       <c r="H68" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I68" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J68" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>205</v>
       </c>
@@ -6052,8 +6553,14 @@
       <c r="H69" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I69" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J69" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>207</v>
       </c>
@@ -6078,8 +6585,14 @@
       <c r="H70" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I70" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J70" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>210</v>
       </c>
@@ -6104,8 +6617,14 @@
       <c r="H71" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I71" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>213</v>
       </c>
@@ -6127,8 +6646,14 @@
       <c r="H72" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I72" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J72" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>215</v>
       </c>
@@ -6150,8 +6675,14 @@
       <c r="H73" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J73" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>217</v>
       </c>
@@ -6173,8 +6704,14 @@
       <c r="H74" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I74" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>219</v>
       </c>
@@ -6196,8 +6733,14 @@
       <c r="H75" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I75" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J75" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>221</v>
       </c>
@@ -6219,8 +6762,14 @@
       <c r="H76" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I76" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>223</v>
       </c>
@@ -6245,8 +6794,14 @@
       <c r="H77" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I77" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J77" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>226</v>
       </c>
@@ -6271,8 +6826,14 @@
       <c r="H78" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I78" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J78" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>229</v>
       </c>
@@ -6297,8 +6858,14 @@
       <c r="H79" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I79" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J79" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>232</v>
       </c>
@@ -6323,8 +6890,14 @@
       <c r="H80" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I80" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J80" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>234</v>
       </c>
@@ -6349,8 +6922,14 @@
       <c r="H81" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I81" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J81" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>237</v>
       </c>
@@ -6372,8 +6951,14 @@
       <c r="H82" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I82" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>239</v>
       </c>
@@ -6395,8 +6980,14 @@
       <c r="H83" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I83" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J83" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>241</v>
       </c>
@@ -6418,8 +7009,14 @@
       <c r="H84" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I84" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J84" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>244</v>
       </c>
@@ -6441,8 +7038,14 @@
       <c r="H85" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I85" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J85" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>246</v>
       </c>
@@ -6467,8 +7070,14 @@
       <c r="H86" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I86" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J86" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -6490,8 +7099,14 @@
       <c r="H87" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I87" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J87" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>250</v>
       </c>
@@ -6513,8 +7128,14 @@
       <c r="H88" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I88" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J88" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -6539,8 +7160,14 @@
       <c r="H89" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I89" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J89" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -6562,8 +7189,14 @@
       <c r="H90" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I90" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J90" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>257</v>
       </c>
@@ -6585,8 +7218,14 @@
       <c r="H91" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I91" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J91" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -6611,8 +7250,14 @@
       <c r="H92" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I92" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J92" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -6634,8 +7279,14 @@
       <c r="G93">
         <v>251</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I93" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -6660,8 +7311,14 @@
       <c r="H94" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I94" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J94" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>268</v>
       </c>
@@ -6683,8 +7340,14 @@
       <c r="H95" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I95" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>271</v>
       </c>
@@ -6706,8 +7369,14 @@
       <c r="G96">
         <v>388</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I96" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>273</v>
       </c>
@@ -6729,8 +7398,14 @@
       <c r="H97" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I97" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>276</v>
       </c>
@@ -6752,8 +7427,14 @@
       <c r="H98" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I98" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>278</v>
       </c>
@@ -6775,8 +7456,14 @@
       <c r="H99" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I99" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>280</v>
       </c>
@@ -6801,8 +7488,14 @@
       <c r="H100" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I100" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>282</v>
       </c>
@@ -6824,8 +7517,14 @@
       <c r="G101">
         <v>262</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I101" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -6850,8 +7549,14 @@
       <c r="H102" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I102" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>286</v>
       </c>
@@ -6876,8 +7581,14 @@
       <c r="H103" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I103" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>289</v>
       </c>
@@ -6902,8 +7613,14 @@
       <c r="H104" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I104" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J104" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>292</v>
       </c>
@@ -6925,8 +7642,14 @@
       <c r="G105">
         <v>473</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I105" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>295</v>
       </c>
@@ -6948,8 +7671,14 @@
       <c r="H106" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I106" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>297</v>
       </c>
@@ -6974,8 +7703,14 @@
       <c r="H107" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I107" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J107" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>299</v>
       </c>
@@ -6997,8 +7732,14 @@
       <c r="H108" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I108" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J108" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>301</v>
       </c>
@@ -7023,8 +7764,14 @@
       <c r="H109" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I109" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J109" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>303</v>
       </c>
@@ -7046,8 +7793,14 @@
       <c r="H110" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I110" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J110" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>305</v>
       </c>
@@ -7072,8 +7825,14 @@
       <c r="H111" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I111" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J111" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>307</v>
       </c>
@@ -7095,8 +7854,14 @@
       <c r="H112" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I112" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>309</v>
       </c>
@@ -7121,8 +7886,14 @@
       <c r="H113" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I113" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J113" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>312</v>
       </c>
@@ -7147,8 +7918,14 @@
       <c r="H114" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I114" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J114" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>315</v>
       </c>
@@ -7173,8 +7950,14 @@
       <c r="H115" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I115" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>317</v>
       </c>
@@ -7196,8 +7979,14 @@
       <c r="H116" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I116" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J116" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>319</v>
       </c>
@@ -7222,8 +8011,14 @@
       <c r="H117" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I117" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J117" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>321</v>
       </c>
@@ -7245,8 +8040,14 @@
       <c r="H118" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I118" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J118" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>324</v>
       </c>
@@ -7271,8 +8072,14 @@
       <c r="H119" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I119" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J119" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>326</v>
       </c>
@@ -7297,8 +8104,14 @@
       <c r="H120" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I120" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J120" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>328</v>
       </c>
@@ -7323,8 +8136,14 @@
       <c r="H121" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I121" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J121" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>330</v>
       </c>
@@ -7346,8 +8165,14 @@
       <c r="G122">
         <v>101</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I122" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J122" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>332</v>
       </c>
@@ -7369,8 +8194,14 @@
       <c r="H123" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I123" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J123" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>334</v>
       </c>
@@ -7392,8 +8223,14 @@
       <c r="H124" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I124" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J124" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>336</v>
       </c>
@@ -7415,8 +8252,14 @@
       <c r="H125" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I125" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J125" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>338</v>
       </c>
@@ -7438,8 +8281,14 @@
       <c r="H126" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I126" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J126" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>340</v>
       </c>
@@ -7461,8 +8310,14 @@
       <c r="H127" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I127" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J127" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>343</v>
       </c>
@@ -7481,8 +8336,14 @@
       <c r="G128">
         <v>326</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I128" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J128" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>346</v>
       </c>
@@ -7507,8 +8368,14 @@
       <c r="H129" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I129" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J129" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>348</v>
       </c>
@@ -7533,8 +8400,14 @@
       <c r="H130" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I130" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J130" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>351</v>
       </c>
@@ -7559,8 +8432,14 @@
       <c r="H131" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I131" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>353</v>
       </c>
@@ -7585,8 +8464,14 @@
       <c r="H132" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I132" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J132" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>355</v>
       </c>
@@ -7608,8 +8493,14 @@
       <c r="H133" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I133" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>357</v>
       </c>
@@ -7631,8 +8522,14 @@
       <c r="H134" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I134" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J134" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>359</v>
       </c>
@@ -7657,8 +8554,14 @@
       <c r="H135" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I135" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>361</v>
       </c>
@@ -7680,8 +8583,14 @@
       <c r="H136" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I136" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>364</v>
       </c>
@@ -7703,8 +8612,14 @@
       <c r="H137" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I137" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>366</v>
       </c>
@@ -7729,8 +8644,14 @@
       <c r="H138" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I138" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>368</v>
       </c>
@@ -7755,8 +8676,14 @@
       <c r="H139" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I139" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>371</v>
       </c>
@@ -7781,8 +8708,14 @@
       <c r="H140" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I140" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>373</v>
       </c>
@@ -7804,8 +8737,14 @@
       <c r="H141" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I141" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>375</v>
       </c>
@@ -7830,8 +8769,14 @@
       <c r="H142" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I142" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J142" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>377</v>
       </c>
@@ -7856,8 +8801,14 @@
       <c r="H143" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I143" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>379</v>
       </c>
@@ -7879,8 +8830,14 @@
       <c r="G144">
         <v>420</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I144" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>381</v>
       </c>
@@ -7899,8 +8856,14 @@
       <c r="G145">
         <v>59</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I145" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>383</v>
       </c>
@@ -7919,8 +8882,14 @@
       <c r="G146">
         <v>404</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I146" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>386</v>
       </c>
@@ -7945,8 +8914,14 @@
       <c r="H147" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I147" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>388</v>
       </c>
@@ -7965,8 +8940,14 @@
       <c r="G148">
         <v>295</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I148" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>390</v>
       </c>
@@ -7988,8 +8969,14 @@
       <c r="H149" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I149" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>393</v>
       </c>
@@ -8011,8 +8998,14 @@
       <c r="H150" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I150" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J150" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>395</v>
       </c>
@@ -8037,8 +9030,14 @@
       <c r="H151" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I151" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J151" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>397</v>
       </c>
@@ -8057,8 +9056,14 @@
       <c r="G152">
         <v>168</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I152" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J152" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>399</v>
       </c>
@@ -8080,8 +9085,14 @@
       <c r="H153" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I153" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J153" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>402</v>
       </c>
@@ -8103,8 +9114,14 @@
       <c r="H154" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I154" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J154" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>404</v>
       </c>
@@ -8129,8 +9146,14 @@
       <c r="H155" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I155" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J155" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>406</v>
       </c>
@@ -8152,8 +9175,14 @@
       <c r="H156" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I156" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J156" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>408</v>
       </c>
@@ -8175,8 +9204,14 @@
       <c r="H157" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I157" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>411</v>
       </c>
@@ -8198,8 +9233,14 @@
       <c r="G158">
         <v>446</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I158" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J158" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>413</v>
       </c>
@@ -8221,8 +9262,14 @@
       <c r="H159" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I159" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J159" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>415</v>
       </c>
@@ -8241,8 +9288,14 @@
       <c r="G160">
         <v>398</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I160" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J160" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>417</v>
       </c>
@@ -8264,8 +9317,14 @@
       <c r="G161">
         <v>485</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I161" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J161" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>419</v>
       </c>
@@ -8287,8 +9346,14 @@
       <c r="H162" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I162" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J162" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>421</v>
       </c>
@@ -8310,8 +9375,14 @@
       <c r="H163" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I163" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J163" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>423</v>
       </c>
@@ -8333,8 +9404,14 @@
       <c r="H164" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I164" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J164" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>425</v>
       </c>
@@ -8356,8 +9433,14 @@
       <c r="H165" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I165" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J165" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>428</v>
       </c>
@@ -8379,8 +9462,14 @@
       <c r="H166" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I166" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J166" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>430</v>
       </c>
@@ -8402,8 +9491,14 @@
       <c r="H167" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I167" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>433</v>
       </c>
@@ -8428,8 +9523,14 @@
       <c r="H168" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I168" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J168" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>435</v>
       </c>
@@ -8454,8 +9555,14 @@
       <c r="H169" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I169" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J169" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>437</v>
       </c>
@@ -8477,8 +9584,14 @@
       <c r="H170" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I170" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J170" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>440</v>
       </c>
@@ -8500,8 +9613,14 @@
       <c r="H171" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I171" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J171" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>442</v>
       </c>
@@ -8523,8 +9642,14 @@
       <c r="H172" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I172" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J172" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>445</v>
       </c>
@@ -8546,8 +9671,14 @@
       <c r="H173" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I173" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J173" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>447</v>
       </c>
@@ -8569,8 +9700,14 @@
       <c r="H174" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I174" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J174" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>449</v>
       </c>
@@ -8592,8 +9729,14 @@
       <c r="H175" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I175" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>451</v>
       </c>
@@ -8618,8 +9761,14 @@
       <c r="H176" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I176" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J176" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>453</v>
       </c>
@@ -8641,8 +9790,14 @@
       <c r="H177" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I177" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J177" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>455</v>
       </c>
@@ -8664,8 +9819,14 @@
       <c r="H178" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I178" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J178" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>457</v>
       </c>
@@ -8687,8 +9848,14 @@
       <c r="H179" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I179" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J179" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>459</v>
       </c>
@@ -8713,8 +9880,14 @@
       <c r="H180" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I180" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J180" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>462</v>
       </c>
@@ -8736,8 +9909,14 @@
       <c r="H181" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I181" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J181" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>464</v>
       </c>
@@ -8756,8 +9935,14 @@
       <c r="G182">
         <v>320</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I182" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J182" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>466</v>
       </c>
@@ -8779,8 +9964,14 @@
       <c r="H183" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I183" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J183" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>468</v>
       </c>
@@ -8799,8 +9990,14 @@
       <c r="G184">
         <v>128</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I184" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J184" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>471</v>
       </c>
@@ -8822,8 +10019,14 @@
       <c r="H185" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I185" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J185" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>473</v>
       </c>
@@ -8845,8 +10048,14 @@
       <c r="H186" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I186" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J186" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>475</v>
       </c>
@@ -8871,8 +10080,14 @@
       <c r="H187" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I187" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J187" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>477</v>
       </c>
@@ -8894,8 +10109,14 @@
       <c r="H188" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I188" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J188" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>479</v>
       </c>
@@ -8920,8 +10141,14 @@
       <c r="H189" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I189" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J189" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>482</v>
       </c>
@@ -8946,8 +10173,14 @@
       <c r="H190" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I190" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J190" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>484</v>
       </c>
@@ -8969,8 +10202,14 @@
       <c r="H191" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I191" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J191" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>486</v>
       </c>
@@ -8989,8 +10228,14 @@
       <c r="G192">
         <v>459</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I192" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J192" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>488</v>
       </c>
@@ -9015,8 +10260,14 @@
       <c r="H193" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I193" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J193" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>491</v>
       </c>
@@ -9038,8 +10289,14 @@
       <c r="H194" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I194" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J194" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>493</v>
       </c>
@@ -9061,8 +10318,14 @@
       <c r="H195" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I195" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J195" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>495</v>
       </c>
@@ -9084,8 +10347,14 @@
       <c r="H196" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I196" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J196" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>497</v>
       </c>
@@ -9107,8 +10376,14 @@
       <c r="H197" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I197" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J197" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>499</v>
       </c>
@@ -9133,8 +10408,14 @@
       <c r="H198" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I198" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J198" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>501</v>
       </c>
@@ -9153,8 +10434,14 @@
       <c r="G199">
         <v>68</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I199" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J199" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>503</v>
       </c>
@@ -9176,8 +10463,14 @@
       <c r="H200" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I200" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J200" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>506</v>
       </c>
@@ -9202,8 +10495,14 @@
       <c r="H201" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I201" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J201" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>508</v>
       </c>
@@ -9228,8 +10527,14 @@
       <c r="H202" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I202" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J202" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>510</v>
       </c>
@@ -9254,8 +10559,14 @@
       <c r="H203" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I203" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J203" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>512</v>
       </c>
@@ -9277,8 +10588,14 @@
       <c r="H204" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I204" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J204" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>514</v>
       </c>
@@ -9303,8 +10620,14 @@
       <c r="H205" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I205" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J205" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>516</v>
       </c>
@@ -9326,8 +10649,14 @@
       <c r="H206" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I206" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J206" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>518</v>
       </c>
@@ -9349,8 +10678,14 @@
       <c r="H207" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I207" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J207" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>521</v>
       </c>
@@ -9375,8 +10710,14 @@
       <c r="H208" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I208" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J208" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>523</v>
       </c>
@@ -9401,8 +10742,14 @@
       <c r="H209" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I209" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J209" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>525</v>
       </c>
@@ -9424,8 +10771,14 @@
       <c r="H210" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I210" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J210" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>527</v>
       </c>
@@ -9450,8 +10803,14 @@
       <c r="H211" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I211" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J211" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>531</v>
       </c>
@@ -9476,8 +10835,14 @@
       <c r="H212" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I212" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J212" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>534</v>
       </c>
@@ -9502,8 +10867,14 @@
       <c r="H213" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I213" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J213" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>537</v>
       </c>
@@ -9528,8 +10899,14 @@
       <c r="H214" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I214" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J214" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>540</v>
       </c>
@@ -9554,8 +10931,14 @@
       <c r="H215" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I215" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J215" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>543</v>
       </c>
@@ -9580,8 +10963,14 @@
       <c r="H216" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I216" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J216" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>546</v>
       </c>
@@ -9603,8 +10992,14 @@
       <c r="G217">
         <v>961</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I217" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J217" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>549</v>
       </c>
@@ -9629,8 +11024,14 @@
       <c r="H218" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I218" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J218" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>552</v>
       </c>
@@ -9655,8 +11056,14 @@
       <c r="H219" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I219" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J219" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>555</v>
       </c>
@@ -9681,8 +11088,14 @@
       <c r="H220" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I220" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J220" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>558</v>
       </c>
@@ -9707,8 +11120,14 @@
       <c r="H221" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I221" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J221" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>561</v>
       </c>
@@ -9733,8 +11152,14 @@
       <c r="H222" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I222" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J222" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>564</v>
       </c>
@@ -9759,8 +11184,14 @@
       <c r="H223" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I223" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>567</v>
       </c>
@@ -9785,8 +11216,14 @@
       <c r="H224" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I224" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J224" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>570</v>
       </c>
@@ -9808,8 +11245,14 @@
       <c r="G225">
         <v>892</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I225" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J225" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>573</v>
       </c>
@@ -9834,8 +11277,14 @@
       <c r="H226" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I226" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J226" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>576</v>
       </c>
@@ -9860,8 +11309,14 @@
       <c r="H227" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I227" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J227" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>579</v>
       </c>
@@ -9886,8 +11341,14 @@
       <c r="H228" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I228" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J228" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>582</v>
       </c>
@@ -9912,8 +11373,14 @@
       <c r="H229" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I229" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J229" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>585</v>
       </c>
@@ -9938,8 +11405,14 @@
       <c r="H230" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I230" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J230" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>588</v>
       </c>
@@ -9964,8 +11437,14 @@
       <c r="H231" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I231" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J231" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>591</v>
       </c>
@@ -9990,8 +11469,14 @@
       <c r="H232" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I232" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J232" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>594</v>
       </c>
@@ -10013,8 +11498,14 @@
       <c r="G233">
         <v>757</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I233" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J233" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>597</v>
       </c>
@@ -10039,8 +11530,14 @@
       <c r="H234" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I234" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J234" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>600</v>
       </c>
@@ -10065,8 +11562,14 @@
       <c r="H235" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I235" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J235" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>603</v>
       </c>
@@ -10091,8 +11594,14 @@
       <c r="H236" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I236" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J236" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>606</v>
       </c>
@@ -10117,8 +11626,14 @@
       <c r="H237" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I237" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J237" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>609</v>
       </c>
@@ -10143,8 +11658,14 @@
       <c r="H238" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I238" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J238" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>612</v>
       </c>
@@ -10169,8 +11690,14 @@
       <c r="H239" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I239" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J239" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>615</v>
       </c>
@@ -10192,8 +11719,14 @@
       <c r="G240">
         <v>494</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I240" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J240" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>618</v>
       </c>
@@ -10218,8 +11751,14 @@
       <c r="H241" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I241" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J241" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>621</v>
       </c>
@@ -10244,8 +11783,14 @@
       <c r="H242" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I242" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J242" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>624</v>
       </c>
@@ -10270,8 +11815,14 @@
       <c r="H243" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I243" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J243" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>627</v>
       </c>
@@ -10296,8 +11847,14 @@
       <c r="H244" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I244" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J244" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>630</v>
       </c>
@@ -10319,8 +11876,14 @@
       <c r="G245">
         <v>315</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I245" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J245" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>633</v>
       </c>
@@ -10345,8 +11908,14 @@
       <c r="H246" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I246" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J246" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>636</v>
       </c>
@@ -10371,8 +11940,14 @@
       <c r="H247" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I247" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J247" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>639</v>
       </c>
@@ -10397,8 +11972,14 @@
       <c r="H248" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="249" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I248" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J248" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>642</v>
       </c>
@@ -10423,8 +12004,14 @@
       <c r="H249" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I249" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J249" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>645</v>
       </c>
@@ -10449,8 +12036,14 @@
       <c r="H250" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I250" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J250" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>648</v>
       </c>
@@ -10475,8 +12068,14 @@
       <c r="H251" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I251" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J251" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>651</v>
       </c>
@@ -10501,8 +12100,14 @@
       <c r="H252" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I252" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J252" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>654</v>
       </c>
@@ -10527,8 +12132,14 @@
       <c r="H253" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I253" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J253" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>657</v>
       </c>
@@ -10553,8 +12164,14 @@
       <c r="H254" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="255" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I254" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J254" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>660</v>
       </c>
@@ -10579,8 +12196,14 @@
       <c r="H255" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="256" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I255" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J255" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>663</v>
       </c>
@@ -10605,8 +12228,14 @@
       <c r="H256" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="257" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I256" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J256" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>666</v>
       </c>
@@ -10631,8 +12260,14 @@
       <c r="H257" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I257" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J257" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>669</v>
       </c>
@@ -10657,8 +12292,14 @@
       <c r="H258" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I258" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J258" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>672</v>
       </c>
@@ -10683,8 +12324,14 @@
       <c r="H259" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="260" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I259" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J259" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>675</v>
       </c>
@@ -10709,8 +12356,14 @@
       <c r="H260" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="261" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I260" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J260" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>678</v>
       </c>
@@ -10735,8 +12388,14 @@
       <c r="H261" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="262" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I261" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J261" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>681</v>
       </c>
@@ -10758,8 +12417,14 @@
       <c r="G262">
         <v>169</v>
       </c>
-    </row>
-    <row r="263" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I262" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J262" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>684</v>
       </c>
@@ -10784,8 +12449,14 @@
       <c r="H263" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="264" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I263" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J263" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>687</v>
       </c>
@@ -10807,8 +12478,14 @@
       <c r="G264">
         <v>253</v>
       </c>
-    </row>
-    <row r="265" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I264" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J264" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>690</v>
       </c>
@@ -10833,8 +12510,14 @@
       <c r="H265" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I265" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J265" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>693</v>
       </c>
@@ -10859,8 +12542,14 @@
       <c r="H266" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I266" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J266" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>696</v>
       </c>
@@ -10885,8 +12574,14 @@
       <c r="H267" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="268" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I267" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J267" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>699</v>
       </c>
@@ -10911,8 +12606,14 @@
       <c r="H268" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="269" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I268" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J268" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>702</v>
       </c>
@@ -10937,8 +12638,14 @@
       <c r="H269" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I269" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J269" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>705</v>
       </c>
@@ -10963,8 +12670,14 @@
       <c r="H270" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="271" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I270" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J270" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>708</v>
       </c>
@@ -10989,8 +12702,14 @@
       <c r="H271" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="272" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I271" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J271" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>711</v>
       </c>
@@ -11015,8 +12734,14 @@
       <c r="H272" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I272" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J272" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>714</v>
       </c>
@@ -11041,8 +12766,14 @@
       <c r="H273" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I273" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J273" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>717</v>
       </c>
@@ -11067,8 +12798,14 @@
       <c r="H274" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I274" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J274" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>720</v>
       </c>
@@ -11093,8 +12830,14 @@
       <c r="H275" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I275" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J275" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>723</v>
       </c>
@@ -11119,8 +12862,14 @@
       <c r="H276" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="277" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I276" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J276" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>726</v>
       </c>
@@ -11145,8 +12894,14 @@
       <c r="H277" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="278" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I277" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J277" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>729</v>
       </c>
@@ -11171,8 +12926,14 @@
       <c r="H278" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="279" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I278" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J278" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>732</v>
       </c>
@@ -11197,8 +12958,14 @@
       <c r="H279" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="280" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I279" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J279" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>735</v>
       </c>
@@ -11223,8 +12990,14 @@
       <c r="H280" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="281" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I280" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J280" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>738</v>
       </c>
@@ -11246,8 +13019,14 @@
       <c r="G281">
         <v>178</v>
       </c>
-    </row>
-    <row r="282" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I281" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J281" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>741</v>
       </c>
@@ -11272,8 +13051,14 @@
       <c r="H282" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="283" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I282" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J282" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>744</v>
       </c>
@@ -11295,8 +13080,14 @@
       <c r="G283">
         <v>661</v>
       </c>
-    </row>
-    <row r="284" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I283" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J283" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>747</v>
       </c>
@@ -11321,8 +13112,14 @@
       <c r="H284" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="285" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I284" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J284" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>750</v>
       </c>
@@ -11347,8 +13144,14 @@
       <c r="H285" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="286" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I285" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J285" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>753</v>
       </c>
@@ -11373,8 +13176,14 @@
       <c r="H286" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="287" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I286" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J286" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>756</v>
       </c>
@@ -11396,8 +13205,14 @@
       <c r="G287">
         <v>727</v>
       </c>
-    </row>
-    <row r="288" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I287" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J287" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>759</v>
       </c>
@@ -11422,8 +13237,14 @@
       <c r="H288" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="289" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I288" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J288" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>762</v>
       </c>
@@ -11445,8 +13266,14 @@
       <c r="G289">
         <v>325</v>
       </c>
-    </row>
-    <row r="290" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I289" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J289" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>765</v>
       </c>
@@ -11471,8 +13298,14 @@
       <c r="H290" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="291" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I290" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J290" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>768</v>
       </c>
@@ -11497,8 +13330,14 @@
       <c r="H291" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="292" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I291" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J291" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>771</v>
       </c>
@@ -11523,8 +13362,14 @@
       <c r="H292" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="293" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I292" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J292" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>774</v>
       </c>
@@ -11549,8 +13394,14 @@
       <c r="H293" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="294" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I293" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J293" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>777</v>
       </c>
@@ -11575,8 +13426,14 @@
       <c r="H294" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="295" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I294" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J294" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>780</v>
       </c>
@@ -11601,8 +13458,14 @@
       <c r="H295" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="296" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I295" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J295" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>783</v>
       </c>
@@ -11627,8 +13490,14 @@
       <c r="H296" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="297" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I296" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J296" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>786</v>
       </c>
@@ -11650,8 +13519,14 @@
       <c r="G297">
         <v>910</v>
       </c>
-    </row>
-    <row r="298" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I297" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J297" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>789</v>
       </c>
@@ -11676,8 +13551,14 @@
       <c r="H298" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="299" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I298" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J298" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>792</v>
       </c>
@@ -11702,8 +13583,14 @@
       <c r="H299" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="300" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I299" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J299" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>795</v>
       </c>
@@ -11728,8 +13615,14 @@
       <c r="H300" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="301" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I300" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J300" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>798</v>
       </c>
@@ -11754,8 +13647,14 @@
       <c r="H301" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="302" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I301" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J301" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>801</v>
       </c>
@@ -11780,8 +13679,14 @@
       <c r="H302" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="303" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I302" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J302" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>804</v>
       </c>
@@ -11803,8 +13708,14 @@
       <c r="G303">
         <v>701</v>
       </c>
-    </row>
-    <row r="304" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I303" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J303" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>807</v>
       </c>
@@ -11829,8 +13740,14 @@
       <c r="H304" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="305" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I304" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J304" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>810</v>
       </c>
@@ -11855,8 +13772,14 @@
       <c r="H305" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="306" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I305" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J305" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>813</v>
       </c>
@@ -11881,8 +13804,14 @@
       <c r="H306" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="307" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I306" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J306" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>816</v>
       </c>
@@ -11907,8 +13836,14 @@
       <c r="H307" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="308" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I307" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J307" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>819</v>
       </c>
@@ -11933,8 +13868,14 @@
       <c r="H308" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="309" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I308" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J308" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>822</v>
       </c>
@@ -11959,8 +13900,14 @@
       <c r="H309" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="310" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I309" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J309" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>825</v>
       </c>
@@ -11985,8 +13932,14 @@
       <c r="H310" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="311" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I310" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J310" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>828</v>
       </c>
@@ -12011,8 +13964,14 @@
       <c r="H311" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="312" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I311" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J311" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>831</v>
       </c>
@@ -12034,8 +13993,14 @@
       <c r="G312">
         <v>683</v>
       </c>
-    </row>
-    <row r="313" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I312" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J312" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>834</v>
       </c>
@@ -12060,8 +14025,14 @@
       <c r="H313" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="314" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I313" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J313" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>837</v>
       </c>
@@ -12086,8 +14057,14 @@
       <c r="H314" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="315" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I314" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J314" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>840</v>
       </c>
@@ -12112,8 +14089,14 @@
       <c r="H315" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="316" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I315" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J315" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>843</v>
       </c>
@@ -12135,8 +14118,14 @@
       <c r="G316">
         <v>63</v>
       </c>
-    </row>
-    <row r="317" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I316" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J316" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>846</v>
       </c>
@@ -12161,8 +14150,14 @@
       <c r="H317" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="318" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I317" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J317" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>849</v>
       </c>
@@ -12187,8 +14182,14 @@
       <c r="H318" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="319" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I318" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J318" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>852</v>
       </c>
@@ -12210,8 +14211,14 @@
       <c r="G319">
         <v>835</v>
       </c>
-    </row>
-    <row r="320" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I319" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J319" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>855</v>
       </c>
@@ -12236,8 +14243,14 @@
       <c r="H320" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="321" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I320" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J320" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>858</v>
       </c>
@@ -12262,8 +14275,14 @@
       <c r="H321" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="322" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I321" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J321" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>861</v>
       </c>
@@ -12288,8 +14307,14 @@
       <c r="H322" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="323" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I322" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J322" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>864</v>
       </c>
@@ -12314,8 +14339,14 @@
       <c r="H323" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="324" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I323" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J323" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>867</v>
       </c>
@@ -12340,8 +14371,14 @@
       <c r="H324" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="325" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I324" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J324" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>870</v>
       </c>
@@ -12366,8 +14403,14 @@
       <c r="H325" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="326" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I325" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J325" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>873</v>
       </c>
@@ -12392,8 +14435,14 @@
       <c r="H326" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="327" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I326" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J326" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>876</v>
       </c>
@@ -12418,8 +14467,14 @@
       <c r="H327" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="328" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I327" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J327" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>879</v>
       </c>
@@ -12444,8 +14499,14 @@
       <c r="H328" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="329" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I328" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J328" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>882</v>
       </c>
@@ -12470,8 +14531,14 @@
       <c r="H329" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="330" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I329" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J329" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>885</v>
       </c>
@@ -12496,8 +14563,14 @@
       <c r="H330" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="331" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I330" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J330" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>888</v>
       </c>
@@ -12522,8 +14595,14 @@
       <c r="H331" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="332" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I331" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J331" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>891</v>
       </c>
@@ -12548,8 +14627,14 @@
       <c r="H332" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="333" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I332" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J332" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>894</v>
       </c>
@@ -12574,8 +14659,14 @@
       <c r="H333" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="334" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I333" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J333" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>897</v>
       </c>
@@ -12600,8 +14691,14 @@
       <c r="H334" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="335" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I334" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J334" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>900</v>
       </c>
@@ -12626,8 +14723,14 @@
       <c r="H335" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="336" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I335" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J335" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>903</v>
       </c>
@@ -12652,8 +14755,14 @@
       <c r="H336" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="337" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I336" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J336" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>906</v>
       </c>
@@ -12678,8 +14787,14 @@
       <c r="H337" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="338" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I337" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J337" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>909</v>
       </c>
@@ -12704,8 +14819,14 @@
       <c r="H338" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="339" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I338" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J338" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>912</v>
       </c>
@@ -12730,8 +14851,14 @@
       <c r="H339" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="340" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I339" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J339" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="340" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>915</v>
       </c>
@@ -12753,8 +14880,14 @@
       <c r="G340">
         <v>242</v>
       </c>
-    </row>
-    <row r="341" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I340" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J340" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>918</v>
       </c>
@@ -12776,8 +14909,14 @@
       <c r="G341">
         <v>967</v>
       </c>
-    </row>
-    <row r="342" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I341" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J341" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>921</v>
       </c>
@@ -12802,8 +14941,14 @@
       <c r="H342" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="343" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I342" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J342" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="343" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>924</v>
       </c>
@@ -12828,8 +14973,14 @@
       <c r="H343" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="344" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I343" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J343" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>927</v>
       </c>
@@ -12854,8 +15005,14 @@
       <c r="H344" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="345" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I344" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J344" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>930</v>
       </c>
@@ -12880,8 +15037,14 @@
       <c r="H345" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="346" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I345" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J345" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>933</v>
       </c>
@@ -12906,8 +15069,14 @@
       <c r="H346" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="347" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I346" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J346" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>936</v>
       </c>
@@ -12932,8 +15101,14 @@
       <c r="H347" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="348" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I347" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J347" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="348" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>939</v>
       </c>
@@ -12955,8 +15130,14 @@
       <c r="G348">
         <v>437</v>
       </c>
-    </row>
-    <row r="349" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I348" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J348" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>942</v>
       </c>
@@ -12978,8 +15159,14 @@
       <c r="G349">
         <v>247</v>
       </c>
-    </row>
-    <row r="350" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I349" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J349" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>945</v>
       </c>
@@ -13004,8 +15191,14 @@
       <c r="H350" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="351" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I350" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J350" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>948</v>
       </c>
@@ -13030,8 +15223,14 @@
       <c r="H351" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="352" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I351" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J351" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="352" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>951</v>
       </c>
@@ -13056,8 +15255,14 @@
       <c r="H352" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="353" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I352" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J352" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>954</v>
       </c>
@@ -13079,8 +15284,14 @@
       <c r="G353">
         <v>15</v>
       </c>
-    </row>
-    <row r="354" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I353" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J353" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>957</v>
       </c>
@@ -13105,8 +15316,14 @@
       <c r="H354" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="355" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I354" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J354" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>960</v>
       </c>
@@ -13131,8 +15348,14 @@
       <c r="H355" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="356" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I355" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J355" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="356" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>963</v>
       </c>
@@ -13157,8 +15380,14 @@
       <c r="H356" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="357" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I356" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J356" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>966</v>
       </c>
@@ -13183,8 +15412,14 @@
       <c r="H357" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="358" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I357" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="358" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>969</v>
       </c>
@@ -13209,8 +15444,14 @@
       <c r="H358" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="359" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I358" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J358" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="359" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>972</v>
       </c>
@@ -13235,8 +15476,14 @@
       <c r="H359" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="360" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I359" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J359" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>975</v>
       </c>
@@ -13261,8 +15508,14 @@
       <c r="H360" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="361" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I360" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J360" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>978</v>
       </c>
@@ -13287,8 +15540,14 @@
       <c r="H361" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="362" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I361" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J361" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>981</v>
       </c>
@@ -13310,8 +15569,14 @@
       <c r="G362">
         <v>88</v>
       </c>
-    </row>
-    <row r="363" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I362" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J362" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>984</v>
       </c>
@@ -13333,8 +15598,14 @@
       <c r="G363">
         <v>234</v>
       </c>
-    </row>
-    <row r="364" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I363" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J363" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>987</v>
       </c>
@@ -13359,8 +15630,14 @@
       <c r="H364" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="365" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I364" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>990</v>
       </c>
@@ -13385,8 +15662,14 @@
       <c r="H365" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="366" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I365" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J365" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>993</v>
       </c>
@@ -13408,8 +15691,14 @@
       <c r="G366">
         <v>353</v>
       </c>
-    </row>
-    <row r="367" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I366" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J366" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>996</v>
       </c>
@@ -13434,8 +15723,14 @@
       <c r="H367" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="368" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I367" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J367" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>999</v>
       </c>
@@ -13460,8 +15755,14 @@
       <c r="H368" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="369" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I368" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J368" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1002</v>
       </c>
@@ -13486,8 +15787,14 @@
       <c r="H369" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="370" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I369" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J369" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1005</v>
       </c>
@@ -13512,8 +15819,14 @@
       <c r="H370" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="371" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I370" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J370" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1008</v>
       </c>
@@ -13538,8 +15851,14 @@
       <c r="H371" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="372" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I371" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J371" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1011</v>
       </c>
@@ -13564,8 +15883,14 @@
       <c r="H372" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="373" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I372" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J372" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1014</v>
       </c>
@@ -13590,8 +15915,14 @@
       <c r="H373" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="374" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I373" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J373" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1017</v>
       </c>
@@ -13616,8 +15947,14 @@
       <c r="H374" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="375" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I374" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J374" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1020</v>
       </c>
@@ -13642,8 +15979,14 @@
       <c r="H375" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="376" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I375" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J375" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1023</v>
       </c>
@@ -13665,8 +16008,14 @@
       <c r="G376">
         <v>780</v>
       </c>
-    </row>
-    <row r="377" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I376" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J376" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1026</v>
       </c>
@@ -13688,8 +16037,14 @@
       <c r="G377">
         <v>443</v>
       </c>
-    </row>
-    <row r="378" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I377" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J377" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1029</v>
       </c>
@@ -13711,8 +16066,14 @@
       <c r="G378">
         <v>111</v>
       </c>
-    </row>
-    <row r="379" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I378" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J378" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>1032</v>
       </c>
@@ -13734,8 +16095,14 @@
       <c r="G379">
         <v>106</v>
       </c>
-    </row>
-    <row r="380" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I379" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J379" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1035</v>
       </c>
@@ -13760,8 +16127,14 @@
       <c r="H380" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="381" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I380" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J380" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1038</v>
       </c>
@@ -13786,8 +16159,14 @@
       <c r="H381" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="382" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I381" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J381" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1041</v>
       </c>
@@ -13809,8 +16188,14 @@
       <c r="G382">
         <v>614</v>
       </c>
-    </row>
-    <row r="383" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I382" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J382" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>1044</v>
       </c>
@@ -13835,8 +16220,14 @@
       <c r="H383" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="384" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I383" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J383" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>1047</v>
       </c>
@@ -13858,8 +16249,14 @@
       <c r="G384">
         <v>999</v>
       </c>
-    </row>
-    <row r="385" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I384" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J384" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1050</v>
       </c>
@@ -13884,8 +16281,14 @@
       <c r="H385" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="386" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I385" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J385" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>1053</v>
       </c>
@@ -13910,8 +16313,14 @@
       <c r="H386" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="387" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I386" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J386" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>1056</v>
       </c>
@@ -13936,8 +16345,14 @@
       <c r="H387" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="388" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I387" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J387" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>1059</v>
       </c>
@@ -13962,8 +16377,14 @@
       <c r="H388" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="389" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I388" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J388" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1062</v>
       </c>
@@ -13988,8 +16409,14 @@
       <c r="H389" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="390" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I389" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J389" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>1065</v>
       </c>
@@ -14011,8 +16438,14 @@
       <c r="G390">
         <v>257</v>
       </c>
-    </row>
-    <row r="391" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I390" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J390" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>1068</v>
       </c>
@@ -14037,8 +16470,14 @@
       <c r="H391" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="392" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I391" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J391" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1071</v>
       </c>
@@ -14063,8 +16502,14 @@
       <c r="H392" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="393" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I392" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J392" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>1074</v>
       </c>
@@ -14089,8 +16534,14 @@
       <c r="H393" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="394" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I393" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J393" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>1077</v>
       </c>
@@ -14115,8 +16566,14 @@
       <c r="H394" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="395" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I394" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J394" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>1080</v>
       </c>
@@ -14141,8 +16598,14 @@
       <c r="H395" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="396" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I395" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J395" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="396" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>1083</v>
       </c>
@@ -14164,8 +16627,14 @@
       <c r="G396">
         <v>363</v>
       </c>
-    </row>
-    <row r="397" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I396" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J396" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>1086</v>
       </c>
@@ -14190,8 +16659,14 @@
       <c r="H397" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="398" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I397" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J397" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>1089</v>
       </c>
@@ -14213,8 +16688,14 @@
       <c r="G398">
         <v>997</v>
       </c>
-    </row>
-    <row r="399" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I398" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J398" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>1092</v>
       </c>
@@ -14239,8 +16720,14 @@
       <c r="H399" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="400" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I399" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J399" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>1095</v>
       </c>
@@ -14265,8 +16752,14 @@
       <c r="H400" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="401" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I400" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J400" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1098</v>
       </c>
@@ -14291,8 +16784,14 @@
       <c r="H401" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="402" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I401" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J401" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>1101</v>
       </c>
@@ -14317,8 +16816,14 @@
       <c r="H402" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="403" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I402" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J402" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>1104</v>
       </c>
@@ -14343,8 +16848,14 @@
       <c r="H403" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="404" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I403" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J403" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>1107</v>
       </c>
@@ -14366,8 +16877,14 @@
       <c r="G404">
         <v>761</v>
       </c>
-    </row>
-    <row r="405" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I404" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J404" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>1110</v>
       </c>
@@ -14392,8 +16909,14 @@
       <c r="H405" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="406" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I405" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J405" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>1113</v>
       </c>
@@ -14418,8 +16941,14 @@
       <c r="H406" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="407" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I406" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J406" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1116</v>
       </c>
@@ -14444,8 +16973,14 @@
       <c r="H407" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="408" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I407" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J407" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>1119</v>
       </c>
@@ -14470,8 +17005,14 @@
       <c r="H408" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="409" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I408" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J408" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>1122</v>
       </c>
@@ -14496,8 +17037,14 @@
       <c r="H409" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="410" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I409" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J409" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="410" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>1125</v>
       </c>
@@ -14522,8 +17069,14 @@
       <c r="H410" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="411" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I410" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J410" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>1128</v>
       </c>
@@ -14548,8 +17101,14 @@
       <c r="H411" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="412" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I411" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J411" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>1131</v>
       </c>
@@ -14571,8 +17130,14 @@
       <c r="G412">
         <v>763</v>
       </c>
-    </row>
-    <row r="413" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I412" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J412" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="413" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>1134</v>
       </c>
@@ -14597,8 +17162,14 @@
       <c r="H413" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="414" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I413" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J413" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>1137</v>
       </c>
@@ -14623,8 +17194,14 @@
       <c r="H414" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="415" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I414" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J414" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>1140</v>
       </c>
@@ -14649,8 +17226,14 @@
       <c r="H415" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="416" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I415" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J415" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>1143</v>
       </c>
@@ -14675,8 +17258,14 @@
       <c r="H416" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="417" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I416" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J416" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>1146</v>
       </c>
@@ -14698,8 +17287,14 @@
       <c r="G417">
         <v>572</v>
       </c>
-    </row>
-    <row r="418" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I417" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J417" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>1149</v>
       </c>
@@ -14724,8 +17319,14 @@
       <c r="H418" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="419" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I418" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J418" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1152</v>
       </c>
@@ -14750,8 +17351,14 @@
       <c r="H419" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="420" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I419" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J419" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>1155</v>
       </c>
@@ -14776,8 +17383,14 @@
       <c r="H420" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="421" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I420" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J420" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>1158</v>
       </c>
@@ -14802,8 +17415,14 @@
       <c r="H421" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="422" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I421" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J421" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>1161</v>
       </c>
@@ -14828,8 +17447,14 @@
       <c r="H422" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="423" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I422" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J422" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>1164</v>
       </c>
@@ -14854,8 +17479,14 @@
       <c r="H423" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="424" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I423" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J423" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>1167</v>
       </c>
@@ -14880,8 +17511,14 @@
       <c r="H424" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="425" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I424" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J424" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>1170</v>
       </c>
@@ -14903,8 +17540,14 @@
       <c r="G425">
         <v>464</v>
       </c>
-    </row>
-    <row r="426" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I425" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J425" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>1173</v>
       </c>
@@ -14929,8 +17572,14 @@
       <c r="H426" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="427" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I426" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J426" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>1176</v>
       </c>
@@ -14955,8 +17604,14 @@
       <c r="H427" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="428" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I427" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J427" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1179</v>
       </c>
@@ -14981,8 +17636,14 @@
       <c r="H428" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="429" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I428" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J428" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>1182</v>
       </c>
@@ -15007,8 +17668,14 @@
       <c r="H429" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="430" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I429" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J429" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1185</v>
       </c>
@@ -15033,8 +17700,14 @@
       <c r="H430" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="431" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I430" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J430" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>1188</v>
       </c>
@@ -15059,8 +17732,14 @@
       <c r="H431" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="432" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I431" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J431" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>1191</v>
       </c>
@@ -15085,8 +17764,14 @@
       <c r="H432" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="433" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I432" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J432" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1194</v>
       </c>
@@ -15111,8 +17796,14 @@
       <c r="H433" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="434" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I433" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J433" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>1197</v>
       </c>
@@ -15137,8 +17828,14 @@
       <c r="H434" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="435" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I434" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J434" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>1200</v>
       </c>
@@ -15163,8 +17860,14 @@
       <c r="H435" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="436" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I435" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J435" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>1203</v>
       </c>
@@ -15189,8 +17892,14 @@
       <c r="H436" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="437" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I436" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J436" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>1206</v>
       </c>
@@ -15215,8 +17924,14 @@
       <c r="H437" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="438" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I437" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J437" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>1209</v>
       </c>
@@ -15241,8 +17956,14 @@
       <c r="H438" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="439" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I438" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J438" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>1212</v>
       </c>
@@ -15267,8 +17988,14 @@
       <c r="H439" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="440" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I439" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J439" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>1215</v>
       </c>
@@ -15293,8 +18020,14 @@
       <c r="H440" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="441" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I440" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J440" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>1218</v>
       </c>
@@ -15319,8 +18052,14 @@
       <c r="H441" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="442" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I441" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J441" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>1221</v>
       </c>
@@ -15345,8 +18084,14 @@
       <c r="H442" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="443" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I442" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J442" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>1224</v>
       </c>
@@ -15371,8 +18116,14 @@
       <c r="H443" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="444" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I443" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J443" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>1227</v>
       </c>
@@ -15397,8 +18148,14 @@
       <c r="H444" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="445" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I444" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J444" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>1230</v>
       </c>
@@ -15423,8 +18180,14 @@
       <c r="H445" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="446" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I445" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J445" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>1233</v>
       </c>
@@ -15449,8 +18212,14 @@
       <c r="H446" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="447" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I446" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J446" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>1236</v>
       </c>
@@ -15475,8 +18244,14 @@
       <c r="H447" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="448" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I447" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J447" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1239</v>
       </c>
@@ -15498,8 +18273,14 @@
       <c r="G448">
         <v>130</v>
       </c>
-    </row>
-    <row r="449" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I448" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J448" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1242</v>
       </c>
@@ -15524,8 +18305,14 @@
       <c r="H449" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="450" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I449" t="s">
+        <v>1432</v>
+      </c>
+      <c r="J449" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>1245</v>
       </c>
@@ -15550,8 +18337,14 @@
       <c r="H450" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="451" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I450" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J450" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>1248</v>
       </c>
@@ -15576,8 +18369,14 @@
       <c r="H451" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="452" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I451" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J451" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>1251</v>
       </c>
@@ -15602,8 +18401,14 @@
       <c r="H452" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="453" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I452" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J452" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1254</v>
       </c>
@@ -15628,8 +18433,14 @@
       <c r="H453" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="454" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I453" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J453" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>1257</v>
       </c>
@@ -15654,8 +18465,14 @@
       <c r="H454" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="455" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I454" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J454" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="455" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>1260</v>
       </c>
@@ -15680,8 +18497,14 @@
       <c r="H455" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="456" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I455" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J455" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>1263</v>
       </c>
@@ -15706,8 +18529,14 @@
       <c r="H456" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="457" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I456" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J456" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>1266</v>
       </c>
@@ -15729,8 +18558,14 @@
       <c r="G457">
         <v>150</v>
       </c>
-    </row>
-    <row r="458" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I457" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J457" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>1269</v>
       </c>
@@ -15755,8 +18590,14 @@
       <c r="H458" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="459" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I458" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J458" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>1272</v>
       </c>
@@ -15778,8 +18619,14 @@
       <c r="G459">
         <v>496</v>
       </c>
-    </row>
-    <row r="460" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I459" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J459" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>1275</v>
       </c>
@@ -15801,8 +18648,14 @@
       <c r="G460">
         <v>265</v>
       </c>
-    </row>
-    <row r="461" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I460" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J460" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>1278</v>
       </c>
@@ -15827,8 +18680,14 @@
       <c r="H461" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="462" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I461" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J461" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>1281</v>
       </c>
@@ -15853,8 +18712,14 @@
       <c r="H462" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="463" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I462" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J462" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>1284</v>
       </c>
@@ -15879,8 +18744,14 @@
       <c r="H463" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="464" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I463" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J463" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="464" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>1287</v>
       </c>
@@ -15905,8 +18776,14 @@
       <c r="H464" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="465" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I464" t="s">
+        <v>1411</v>
+      </c>
+      <c r="J464" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>1290</v>
       </c>
@@ -15931,8 +18808,14 @@
       <c r="H465" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="466" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I465" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J465" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>1293</v>
       </c>
@@ -15957,8 +18840,14 @@
       <c r="H466" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="467" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I466" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J466" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1296</v>
       </c>
@@ -15980,8 +18869,14 @@
       <c r="G467">
         <v>131</v>
       </c>
-    </row>
-    <row r="468" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I467" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J467" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>1299</v>
       </c>
@@ -16006,8 +18901,14 @@
       <c r="H468" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="469" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I468" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J468" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>1302</v>
       </c>
@@ -16032,8 +18933,14 @@
       <c r="H469" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="470" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I469" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J469" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>1305</v>
       </c>
@@ -16058,8 +18965,14 @@
       <c r="H470" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="471" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I470" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J470" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>1308</v>
       </c>
@@ -16084,8 +18997,14 @@
       <c r="H471" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="472" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I471" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J471" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>1311</v>
       </c>
@@ -16110,8 +19029,14 @@
       <c r="H472" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="473" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I472" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J472" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>1314</v>
       </c>
@@ -16136,8 +19061,14 @@
       <c r="H473" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="474" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I473" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J473" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>1317</v>
       </c>
@@ -16162,8 +19093,14 @@
       <c r="H474" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="475" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I474" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J474" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>1320</v>
       </c>
@@ -16188,8 +19125,14 @@
       <c r="H475" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="476" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I475" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J475" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>1323</v>
       </c>
@@ -16214,8 +19157,14 @@
       <c r="H476" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="477" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I476" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J476" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>1326</v>
       </c>
@@ -16240,8 +19189,14 @@
       <c r="H477" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="478" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I477" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J477" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>1329</v>
       </c>
@@ -16266,8 +19221,14 @@
       <c r="H478" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="479" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I478" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J478" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>1332</v>
       </c>
@@ -16292,8 +19253,14 @@
       <c r="H479" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="480" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I479" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>1335</v>
       </c>
@@ -16318,8 +19285,14 @@
       <c r="H480" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="481" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I480" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J480" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>1338</v>
       </c>
@@ -16344,8 +19317,14 @@
       <c r="H481" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="482" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I481" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J481" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>1341</v>
       </c>
@@ -16370,8 +19349,14 @@
       <c r="H482" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="483" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I482" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J482" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>1344</v>
       </c>
@@ -16396,8 +19381,14 @@
       <c r="H483" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="484" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I483" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J483" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>1347</v>
       </c>
@@ -16419,8 +19410,14 @@
       <c r="G484">
         <v>116</v>
       </c>
-    </row>
-    <row r="485" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I484" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J484" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>1350</v>
       </c>
@@ -16445,8 +19442,14 @@
       <c r="H485" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="486" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I485" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J485" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>1353</v>
       </c>
@@ -16468,8 +19471,14 @@
       <c r="G486">
         <v>89</v>
       </c>
-    </row>
-    <row r="487" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I486" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J486" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>1356</v>
       </c>
@@ -16494,8 +19503,14 @@
       <c r="H487" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="488" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I487" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J487" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>1359</v>
       </c>
@@ -16520,8 +19535,14 @@
       <c r="H488" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="489" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I488" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J488" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>1362</v>
       </c>
@@ -16546,8 +19567,14 @@
       <c r="H489" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="490" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I489" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J489" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>1365</v>
       </c>
@@ -16572,8 +19599,14 @@
       <c r="H490" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="491" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I490" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J490" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>1368</v>
       </c>
@@ -16598,8 +19631,14 @@
       <c r="H491" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="492" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I491" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J491" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>1371</v>
       </c>
@@ -16624,8 +19663,14 @@
       <c r="H492" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="493" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I492" t="s">
+        <v>1407</v>
+      </c>
+      <c r="J492" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>1374</v>
       </c>
@@ -16650,8 +19695,14 @@
       <c r="H493" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="494" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I493" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J493" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1377</v>
       </c>
@@ -16676,8 +19727,14 @@
       <c r="H494" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="495" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I494" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J494" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>1380</v>
       </c>
@@ -16702,8 +19759,14 @@
       <c r="H495" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="496" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I495" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J495" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>1383</v>
       </c>
@@ -16728,8 +19791,14 @@
       <c r="H496" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="497" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I496" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J496" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>1386</v>
       </c>
@@ -16754,8 +19823,14 @@
       <c r="H497" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="498" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I497" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J497" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>1389</v>
       </c>
@@ -16777,8 +19852,14 @@
       <c r="G498">
         <v>655</v>
       </c>
-    </row>
-    <row r="499" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I498" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J498" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>1392</v>
       </c>
@@ -16803,8 +19884,14 @@
       <c r="H499" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="500" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I499" t="s">
+        <v>1403</v>
+      </c>
+      <c r="J499" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>1395</v>
       </c>
@@ -16829,8 +19916,14 @@
       <c r="H500" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="501" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I500" t="s">
+        <v>1405</v>
+      </c>
+      <c r="J500" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>1398</v>
       </c>
@@ -16851,6 +19944,12 @@
       </c>
       <c r="G501">
         <v>251</v>
+      </c>
+      <c r="I501" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J501" t="s">
+        <v>1415</v>
       </c>
     </row>
   </sheetData>
